--- a/templates/formation_template.xlsx
+++ b/templates/formation_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9696347E-3225-4386-A22E-7BE6470B35EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AEC37E0-6F28-430B-8664-D035569F46D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C51D75B5-576D-44D8-AA92-323E688AAC37}"/>
   </bookViews>
@@ -778,15 +778,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:colOff>25400</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
+      <xdr:colOff>82550</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>231900</xdr:rowOff>
+      <xdr:rowOff>238250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -815,7 +815,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="114300" y="114300"/>
+          <a:off x="120650" y="120650"/>
           <a:ext cx="654050" cy="727200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
